--- a/Informe tecnico/costos finales.xlsx
+++ b/Informe tecnico/costos finales.xlsx
@@ -1,15 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sena\Monitor-de-consumo\Documentacion-proyecto-Monitor-de-consumo-electrico\Informe tecnico\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650" firstSheet="1" activeTab="2"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="1.Resumen" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="5.Diagrama de gantt" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="costos del equipo de trabajo" sheetId="3" r:id="rId6"/>
-    <sheet state="visible" name="costos estimados para usuarios" sheetId="4" r:id="rId7"/>
+    <sheet name="1.Resumen" sheetId="1" r:id="rId1"/>
+    <sheet name="5.Diagrama de gantt" sheetId="2" r:id="rId2"/>
+    <sheet name="costos del equipo de trabajo" sheetId="3" r:id="rId3"/>
+    <sheet name="costos estimados para usuarios" sheetId="4" r:id="rId4"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="Pz3iwk33jnOiIPCKBtoSzWvzhcyR2oF1QmG3ZwfGeKY="/>
@@ -19,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="136">
   <si>
     <t>Resumen Ejecutivo Ppto</t>
   </si>
@@ -216,9 +224,6 @@
     <t>$8.000.000 – $15.000.000+</t>
   </si>
   <si>
-    <t>Sensor de corriente SCT-013 (hasta 100A)</t>
-  </si>
-  <si>
     <t>Visual Studio Code</t>
   </si>
   <si>
@@ -237,15 +242,9 @@
     <t>Intel Core i9 / AMD Ryzen 9</t>
   </si>
   <si>
-    <t>Fuente de alimentación 5V / 2A</t>
-  </si>
-  <si>
     <t>Firebase</t>
   </si>
   <si>
-    <t>Plan gratuito (Spark)</t>
-  </si>
-  <si>
     <t>gestor de bases de datos</t>
   </si>
   <si>
@@ -261,18 +260,6 @@
     <t>64 GB DDR4/DDR5</t>
   </si>
   <si>
-    <t>Protoboard + cables Dupont</t>
-  </si>
-  <si>
-    <t>1 set</t>
-  </si>
-  <si>
-    <t>Opcional (plan pago Firebase)</t>
-  </si>
-  <si>
-    <t>$20.000 – $40.000/mes si se escala el proyecto</t>
-  </si>
-  <si>
     <t>analista</t>
   </si>
   <si>
@@ -288,9 +275,6 @@
     <t>2 TB SSD NVMe</t>
   </si>
   <si>
-    <t>Resistencias, capacitores y componentes varios</t>
-  </si>
-  <si>
     <t>Total recurso humano</t>
   </si>
   <si>
@@ -336,9 +320,6 @@
     <t>Falabella, Mercado Libre, PC Ware Colombia</t>
   </si>
   <si>
-    <t>Mercado Libre, PC Gamer Tiendas Especializadas, Distribuidores de hardware premium</t>
-  </si>
-  <si>
     <t>costos cel del equipo de desarrollo</t>
   </si>
   <si>
@@ -352,9 +333,6 @@
   </si>
   <si>
     <t>total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$10'500.000 </t>
   </si>
   <si>
     <t>opcion de celular para desarrolladores</t>
@@ -407,19 +385,18 @@
   <si>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
-        <b/>
-        <color theme="1"/>
-        <sz val="11.0"/>
       </rPr>
       <t>HP 240 G9</t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
-        <b val="0"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
       </rPr>
       <t xml:space="preserve"> (Core i5, 8 GB RAM, 512 GB SSD)</t>
     </r>
@@ -433,19 +410,18 @@
   <si>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
-        <b/>
-        <color theme="1"/>
-        <sz val="11.0"/>
       </rPr>
       <t>Dell Inspiron 15</t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
-        <b val="0"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
       </rPr>
       <t xml:space="preserve"> (Core i5, 8 GB RAM)</t>
     </r>
@@ -459,19 +435,18 @@
   <si>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
-        <b/>
-        <color theme="1"/>
-        <sz val="11.0"/>
       </rPr>
       <t>Apple MacBook Air M2</t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
-        <b val="0"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
       </rPr>
       <t xml:space="preserve"> (8 GB RAM, 256 GB SSD)</t>
     </r>
@@ -481,70 +456,136 @@
   </si>
   <si>
     <t>Éxito, Mercado Libre</t>
+  </si>
+  <si>
+    <t>Fuente de alimentación Ac-dc 3.3v Hlk-pm03</t>
+  </si>
+  <si>
+    <t>Cables Jumpers Macho Macho 20 cm</t>
+  </si>
+  <si>
+    <t>Cables Jumpers Macho Hembra 20 cm</t>
+  </si>
+  <si>
+    <t>Medidor de electricidad digital Peacefair PZEM-004T-100A (Sensor)</t>
+  </si>
+  <si>
+    <t>Cable eléctrico encauchetado de 2x14 AWG</t>
+  </si>
+  <si>
+    <t>Cables Jumpers Hembra Hembra 20 cm</t>
+  </si>
+  <si>
+    <t>Cable calibre 14 rojo y negro</t>
+  </si>
+  <si>
+    <t>Conector Jst Macho-Hembra Xh2.54 Xh2.54mm 4</t>
+  </si>
+  <si>
+    <t>Gratis</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="6">
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-[$$-240A]\ * #,##0.00_-;\-[$$-240A]\ * #,##0.00_-;_-[$$-240A]\ * &quot;-&quot;??_-;_-@"/>
     <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;?_-;_-@"/>
-    <numFmt numFmtId="166" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="166" formatCode="_-[$$-240A]\ * #,##0.00_-;\-[$$-240A]\ * #,##0.00_-;_-[$$-240A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="&quot;$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="15">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
-    <font/>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="18.0"/>
+      <sz val="18"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Aptos"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="16.0"/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="10">
@@ -552,7 +593,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -603,20 +644,29 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
-    <border/>
+  <borders count="44">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -626,6 +676,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -640,14 +691,18 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -659,6 +714,8 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -667,6 +724,9 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -675,15 +735,18 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -696,6 +759,7 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -706,6 +770,7 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -714,6 +779,7 @@
       </right>
       <top/>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -722,22 +788,31 @@
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -746,214 +821,656 @@
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+  <cellXfs count="118">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="1" numFmtId="165" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="3" fillId="3" fontId="1" numFmtId="165" xfId="0" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="3" fillId="4" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="3" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="4" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="5" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="3" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="3" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="6" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="3" fillId="6" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="3" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="7" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="3" fillId="7" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="3" fillId="7" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="8" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="3" fillId="8" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="3" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="9" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="6" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="9" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="4" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="9" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="10" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="9" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="11" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="9" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="12" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="13" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="13" fillId="0" fontId="3" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="13" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="13" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="14" fillId="0" fontId="3" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="8" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="8" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="14" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="3" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="8" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="13" fillId="0" fontId="3" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="14" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="8" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="14" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="7" fillId="0" fontId="8" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="15" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="16" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="16" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="16" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="8" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="13" fillId="0" fontId="7" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="7" fillId="0" fontId="1" numFmtId="166" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="9" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="4" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Moneda" xfId="1" builtinId="4"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1143,85 +1660,85 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:C1000"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="2" width="10.71"/>
-    <col customWidth="1" min="3" max="3" width="28.14"/>
-    <col customWidth="1" min="4" max="26" width="10.71"/>
+    <col min="1" max="2" width="10.7109375" customWidth="1"/>
+    <col min="3" max="3" width="28.140625" customWidth="1"/>
+    <col min="4" max="26" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1"/>
-    <row r="2" ht="14.25" customHeight="1">
-      <c r="B2" s="1" t="s">
+    <row r="1" spans="2:3" ht="14.25" customHeight="1"/>
+    <row r="2" spans="2:3" ht="14.25" customHeight="1">
+      <c r="B2" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2"/>
+      <c r="C2" s="44"/>
     </row>
-    <row r="3" ht="14.25" customHeight="1">
-      <c r="B3" s="3" t="s">
+    <row r="3" spans="2:3" ht="14.25" customHeight="1">
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" ht="14.25" customHeight="1">
-      <c r="B4" s="4" t="s">
+    <row r="4" spans="2:3" ht="14.25" customHeight="1">
+      <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="5">
-        <f>'costos del equipo de trabajo'!E12</f>
-        <v>11105000</v>
+      <c r="C4" s="3">
+        <f>'costos del equipo de trabajo'!E16</f>
+        <v>8073997</v>
       </c>
     </row>
-    <row r="5" ht="14.25" customHeight="1">
-      <c r="B5" s="4" t="s">
+    <row r="5" spans="2:3" ht="14.25" customHeight="1">
+      <c r="B5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="4">
         <f>'costos del equipo de trabajo'!I7</f>
-        <v>240000</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="6" ht="14.25" customHeight="1">
-      <c r="B6" s="4" t="s">
+    <row r="6" spans="2:3" ht="14.25" customHeight="1">
+      <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="4">
         <f>'costos del equipo de trabajo'!O8</f>
-        <v>44700000</v>
+        <v>48900000</v>
       </c>
     </row>
-    <row r="7" ht="14.25" customHeight="1">
-      <c r="B7" s="4" t="s">
+    <row r="7" spans="2:3" ht="14.25" customHeight="1">
+      <c r="B7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="6">
-        <v>0.0</v>
+      <c r="C7" s="4">
+        <v>0</v>
       </c>
     </row>
-    <row r="8" ht="14.25" customHeight="1">
-      <c r="C8" s="7">
+    <row r="8" spans="2:3" ht="14.25" customHeight="1">
+      <c r="C8" s="5">
         <f>SUM(C4:C6)</f>
-        <v>56045000</v>
+        <v>56973997</v>
       </c>
     </row>
-    <row r="9" ht="14.25" customHeight="1"/>
-    <row r="10" ht="14.25" customHeight="1"/>
-    <row r="11" ht="14.25" customHeight="1"/>
-    <row r="12" ht="14.25" customHeight="1"/>
-    <row r="13" ht="14.25" customHeight="1"/>
-    <row r="14" ht="14.25" customHeight="1"/>
-    <row r="15" ht="14.25" customHeight="1"/>
-    <row r="16" ht="14.25" customHeight="1"/>
+    <row r="9" spans="2:3" ht="14.25" customHeight="1"/>
+    <row r="10" spans="2:3" ht="14.25" customHeight="1"/>
+    <row r="11" spans="2:3" ht="14.25" customHeight="1"/>
+    <row r="12" spans="2:3" ht="14.25" customHeight="1"/>
+    <row r="13" spans="2:3" ht="14.25" customHeight="1"/>
+    <row r="14" spans="2:3" ht="14.25" customHeight="1"/>
+    <row r="15" spans="2:3" ht="14.25" customHeight="1"/>
+    <row r="16" spans="2:3" ht="14.25" customHeight="1"/>
     <row r="17" ht="14.25" customHeight="1"/>
     <row r="18" ht="14.25" customHeight="1"/>
     <row r="19" ht="14.25" customHeight="1"/>
@@ -2210,934 +2727,930 @@
   <mergeCells count="1">
     <mergeCell ref="B2:C2"/>
   </mergeCells>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:AE1000"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="2" width="10.71"/>
-    <col customWidth="1" min="3" max="3" width="24.71"/>
-    <col customWidth="1" min="4" max="4" width="5.29"/>
-    <col customWidth="1" min="5" max="5" width="5.14"/>
-    <col customWidth="1" min="6" max="6" width="5.0"/>
-    <col customWidth="1" min="7" max="7" width="5.43"/>
-    <col customWidth="1" min="8" max="9" width="5.29"/>
-    <col customWidth="1" min="10" max="10" width="5.14"/>
-    <col customWidth="1" min="11" max="13" width="5.29"/>
-    <col customWidth="1" min="14" max="15" width="5.0"/>
-    <col customWidth="1" min="16" max="17" width="5.29"/>
-    <col customWidth="1" min="18" max="18" width="5.0"/>
-    <col customWidth="1" min="19" max="19" width="5.29"/>
-    <col customWidth="1" min="20" max="20" width="5.14"/>
-    <col customWidth="1" min="21" max="26" width="5.29"/>
-    <col customWidth="1" min="27" max="31" width="5.43"/>
+    <col min="1" max="2" width="10.7109375" customWidth="1"/>
+    <col min="3" max="3" width="24.7109375" customWidth="1"/>
+    <col min="4" max="4" width="5.28515625" customWidth="1"/>
+    <col min="5" max="5" width="5.140625" customWidth="1"/>
+    <col min="6" max="6" width="5" customWidth="1"/>
+    <col min="7" max="7" width="5.42578125" customWidth="1"/>
+    <col min="8" max="9" width="5.28515625" customWidth="1"/>
+    <col min="10" max="10" width="5.140625" customWidth="1"/>
+    <col min="11" max="13" width="5.28515625" customWidth="1"/>
+    <col min="14" max="15" width="5" customWidth="1"/>
+    <col min="16" max="17" width="5.28515625" customWidth="1"/>
+    <col min="18" max="18" width="5" customWidth="1"/>
+    <col min="19" max="19" width="5.28515625" customWidth="1"/>
+    <col min="20" max="20" width="5.140625" customWidth="1"/>
+    <col min="21" max="26" width="5.28515625" customWidth="1"/>
+    <col min="27" max="31" width="5.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1"/>
-    <row r="2" ht="14.25" customHeight="1">
-      <c r="D2" s="8" t="s">
+    <row r="1" spans="2:31" ht="14.25" customHeight="1"/>
+    <row r="2" spans="2:31" ht="14.25" customHeight="1">
+      <c r="D2" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="8" t="s">
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="8" t="s">
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="8" t="s">
+      <c r="M2" s="46"/>
+      <c r="N2" s="46"/>
+      <c r="O2" s="44"/>
+      <c r="P2" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9"/>
-      <c r="S2" s="2"/>
-      <c r="T2" s="8" t="s">
+      <c r="Q2" s="46"/>
+      <c r="R2" s="46"/>
+      <c r="S2" s="44"/>
+      <c r="T2" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="U2" s="9"/>
-      <c r="V2" s="9"/>
-      <c r="W2" s="2"/>
-      <c r="X2" s="8" t="s">
+      <c r="U2" s="46"/>
+      <c r="V2" s="46"/>
+      <c r="W2" s="44"/>
+      <c r="X2" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="Y2" s="9"/>
-      <c r="Z2" s="9"/>
-      <c r="AA2" s="2"/>
-      <c r="AB2" s="8" t="s">
+      <c r="Y2" s="46"/>
+      <c r="Z2" s="46"/>
+      <c r="AA2" s="44"/>
+      <c r="AB2" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="AC2" s="9"/>
-      <c r="AD2" s="9"/>
-      <c r="AE2" s="2"/>
+      <c r="AC2" s="46"/>
+      <c r="AD2" s="46"/>
+      <c r="AE2" s="44"/>
     </row>
-    <row r="3" ht="14.25" customHeight="1">
-      <c r="D3" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="E3" s="10">
-        <v>2.0</v>
-      </c>
-      <c r="F3" s="10">
-        <v>3.0</v>
-      </c>
-      <c r="G3" s="10">
-        <v>4.0</v>
-      </c>
-      <c r="H3" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="I3" s="10">
-        <v>2.0</v>
-      </c>
-      <c r="J3" s="10">
-        <v>3.0</v>
-      </c>
-      <c r="K3" s="10">
-        <v>4.0</v>
-      </c>
-      <c r="L3" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="M3" s="10">
-        <v>2.0</v>
-      </c>
-      <c r="N3" s="10">
-        <v>3.0</v>
-      </c>
-      <c r="O3" s="10">
-        <v>4.0</v>
-      </c>
-      <c r="P3" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="Q3" s="10">
-        <v>2.0</v>
-      </c>
-      <c r="R3" s="10">
-        <v>3.0</v>
-      </c>
-      <c r="S3" s="10">
-        <v>4.0</v>
-      </c>
-      <c r="T3" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="U3" s="10">
-        <v>2.0</v>
-      </c>
-      <c r="V3" s="10">
-        <v>3.0</v>
-      </c>
-      <c r="W3" s="10">
-        <v>4.0</v>
-      </c>
-      <c r="X3" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="Y3" s="10">
-        <v>2.0</v>
-      </c>
-      <c r="Z3" s="10">
-        <v>3.0</v>
-      </c>
-      <c r="AA3" s="10">
-        <v>4.0</v>
-      </c>
-      <c r="AB3" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="AC3" s="10">
-        <v>2.0</v>
-      </c>
-      <c r="AD3" s="10">
-        <v>3.0</v>
-      </c>
-      <c r="AE3" s="10">
-        <v>4.0</v>
+    <row r="3" spans="2:31" ht="14.25" customHeight="1">
+      <c r="D3" s="6">
+        <v>1</v>
+      </c>
+      <c r="E3" s="6">
+        <v>2</v>
+      </c>
+      <c r="F3" s="6">
+        <v>3</v>
+      </c>
+      <c r="G3" s="6">
+        <v>4</v>
+      </c>
+      <c r="H3" s="6">
+        <v>1</v>
+      </c>
+      <c r="I3" s="6">
+        <v>2</v>
+      </c>
+      <c r="J3" s="6">
+        <v>3</v>
+      </c>
+      <c r="K3" s="6">
+        <v>4</v>
+      </c>
+      <c r="L3" s="6">
+        <v>1</v>
+      </c>
+      <c r="M3" s="6">
+        <v>2</v>
+      </c>
+      <c r="N3" s="6">
+        <v>3</v>
+      </c>
+      <c r="O3" s="6">
+        <v>4</v>
+      </c>
+      <c r="P3" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="6">
+        <v>2</v>
+      </c>
+      <c r="R3" s="6">
+        <v>3</v>
+      </c>
+      <c r="S3" s="6">
+        <v>4</v>
+      </c>
+      <c r="T3" s="6">
+        <v>1</v>
+      </c>
+      <c r="U3" s="6">
+        <v>2</v>
+      </c>
+      <c r="V3" s="6">
+        <v>3</v>
+      </c>
+      <c r="W3" s="6">
+        <v>4</v>
+      </c>
+      <c r="X3" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="6">
+        <v>2</v>
+      </c>
+      <c r="Z3" s="6">
+        <v>3</v>
+      </c>
+      <c r="AA3" s="6">
+        <v>4</v>
+      </c>
+      <c r="AB3" s="6">
+        <v>1</v>
+      </c>
+      <c r="AC3" s="6">
+        <v>2</v>
+      </c>
+      <c r="AD3" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE3" s="6">
+        <v>4</v>
       </c>
     </row>
-    <row r="4" ht="14.25" customHeight="1">
-      <c r="B4" s="11" t="s">
+    <row r="4" spans="2:31" ht="14.25" customHeight="1">
+      <c r="B4" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="14"/>
-      <c r="N4" s="14"/>
-      <c r="O4" s="14"/>
-      <c r="P4" s="14"/>
-      <c r="Q4" s="14"/>
-      <c r="R4" s="14"/>
-      <c r="S4" s="14"/>
-      <c r="T4" s="14"/>
-      <c r="U4" s="14"/>
-      <c r="V4" s="14"/>
-      <c r="W4" s="14"/>
-      <c r="X4" s="14"/>
-      <c r="Y4" s="14"/>
-      <c r="Z4" s="14"/>
-      <c r="AA4" s="14"/>
-      <c r="AB4" s="14"/>
-      <c r="AC4" s="14"/>
-      <c r="AD4" s="14"/>
-      <c r="AE4" s="14"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
+      <c r="V4" s="9"/>
+      <c r="W4" s="9"/>
+      <c r="X4" s="9"/>
+      <c r="Y4" s="9"/>
+      <c r="Z4" s="9"/>
+      <c r="AA4" s="9"/>
+      <c r="AB4" s="9"/>
+      <c r="AC4" s="9"/>
+      <c r="AD4" s="9"/>
+      <c r="AE4" s="9"/>
     </row>
-    <row r="5" ht="14.25" customHeight="1">
-      <c r="B5" s="15"/>
-      <c r="C5" s="12" t="s">
+    <row r="5" spans="2:31" ht="14.25" customHeight="1">
+      <c r="B5" s="48"/>
+      <c r="C5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
-      <c r="K5" s="14"/>
-      <c r="L5" s="14"/>
-      <c r="M5" s="14"/>
-      <c r="N5" s="14"/>
-      <c r="O5" s="14"/>
-      <c r="P5" s="14"/>
-      <c r="Q5" s="14"/>
-      <c r="R5" s="14"/>
-      <c r="S5" s="14"/>
-      <c r="T5" s="14"/>
-      <c r="U5" s="14"/>
-      <c r="V5" s="14"/>
-      <c r="W5" s="14"/>
-      <c r="X5" s="14"/>
-      <c r="Y5" s="14"/>
-      <c r="Z5" s="14"/>
-      <c r="AA5" s="14"/>
-      <c r="AB5" s="14"/>
-      <c r="AC5" s="14"/>
-      <c r="AD5" s="14"/>
-      <c r="AE5" s="14"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="9"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="9"/>
+      <c r="W5" s="9"/>
+      <c r="X5" s="9"/>
+      <c r="Y5" s="9"/>
+      <c r="Z5" s="9"/>
+      <c r="AA5" s="9"/>
+      <c r="AB5" s="9"/>
+      <c r="AC5" s="9"/>
+      <c r="AD5" s="9"/>
+      <c r="AE5" s="9"/>
     </row>
-    <row r="6" ht="14.25" customHeight="1">
-      <c r="B6" s="15"/>
-      <c r="C6" s="12" t="s">
+    <row r="6" spans="2:31" ht="14.25" customHeight="1">
+      <c r="B6" s="48"/>
+      <c r="C6" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14"/>
-      <c r="N6" s="14"/>
-      <c r="O6" s="14"/>
-      <c r="P6" s="14"/>
-      <c r="Q6" s="14"/>
-      <c r="R6" s="14"/>
-      <c r="S6" s="14"/>
-      <c r="T6" s="14"/>
-      <c r="U6" s="14"/>
-      <c r="V6" s="14"/>
-      <c r="W6" s="14"/>
-      <c r="X6" s="14"/>
-      <c r="Y6" s="14"/>
-      <c r="Z6" s="14"/>
-      <c r="AA6" s="14"/>
-      <c r="AB6" s="14"/>
-      <c r="AC6" s="14"/>
-      <c r="AD6" s="14"/>
-      <c r="AE6" s="14"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="9"/>
+      <c r="R6" s="9"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="9"/>
+      <c r="U6" s="9"/>
+      <c r="V6" s="9"/>
+      <c r="W6" s="9"/>
+      <c r="X6" s="9"/>
+      <c r="Y6" s="9"/>
+      <c r="Z6" s="9"/>
+      <c r="AA6" s="9"/>
+      <c r="AB6" s="9"/>
+      <c r="AC6" s="9"/>
+      <c r="AD6" s="9"/>
+      <c r="AE6" s="9"/>
     </row>
-    <row r="7" ht="14.25" customHeight="1">
-      <c r="B7" s="16"/>
-      <c r="C7" s="17" t="s">
+    <row r="7" spans="2:31" ht="14.25" customHeight="1">
+      <c r="B7" s="49"/>
+      <c r="C7" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
-      <c r="M7" s="14"/>
-      <c r="N7" s="14"/>
-      <c r="O7" s="14"/>
-      <c r="P7" s="14"/>
-      <c r="Q7" s="14"/>
-      <c r="R7" s="14"/>
-      <c r="S7" s="14"/>
-      <c r="T7" s="14"/>
-      <c r="U7" s="14"/>
-      <c r="V7" s="14"/>
-      <c r="W7" s="14"/>
-      <c r="X7" s="14"/>
-      <c r="Y7" s="14"/>
-      <c r="Z7" s="14"/>
-      <c r="AA7" s="14"/>
-      <c r="AB7" s="14"/>
-      <c r="AC7" s="14"/>
-      <c r="AD7" s="14"/>
-      <c r="AE7" s="14"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="9"/>
+      <c r="S7" s="9"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="9"/>
+      <c r="V7" s="9"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="9"/>
+      <c r="Y7" s="9"/>
+      <c r="Z7" s="9"/>
+      <c r="AA7" s="9"/>
+      <c r="AB7" s="9"/>
+      <c r="AC7" s="9"/>
+      <c r="AD7" s="9"/>
+      <c r="AE7" s="9"/>
     </row>
-    <row r="8" ht="14.25" customHeight="1">
-      <c r="B8" s="11" t="s">
+    <row r="8" spans="2:31" ht="14.25" customHeight="1">
+      <c r="B8" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="14"/>
-      <c r="M8" s="14"/>
-      <c r="N8" s="14"/>
-      <c r="O8" s="14"/>
-      <c r="P8" s="14"/>
-      <c r="Q8" s="14"/>
-      <c r="R8" s="14"/>
-      <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
-      <c r="U8" s="14"/>
-      <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
-      <c r="X8" s="14"/>
-      <c r="Y8" s="14"/>
-      <c r="Z8" s="14"/>
-      <c r="AA8" s="14"/>
-      <c r="AB8" s="14"/>
-      <c r="AC8" s="14"/>
-      <c r="AD8" s="14"/>
-      <c r="AE8" s="14"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="9"/>
+      <c r="R8" s="9"/>
+      <c r="S8" s="9"/>
+      <c r="T8" s="9"/>
+      <c r="U8" s="9"/>
+      <c r="V8" s="9"/>
+      <c r="W8" s="9"/>
+      <c r="X8" s="9"/>
+      <c r="Y8" s="9"/>
+      <c r="Z8" s="9"/>
+      <c r="AA8" s="9"/>
+      <c r="AB8" s="9"/>
+      <c r="AC8" s="9"/>
+      <c r="AD8" s="9"/>
+      <c r="AE8" s="9"/>
     </row>
-    <row r="9" ht="14.25" customHeight="1">
-      <c r="B9" s="15"/>
-      <c r="C9" s="18" t="s">
+    <row r="9" spans="2:31" ht="14.25" customHeight="1">
+      <c r="B9" s="48"/>
+      <c r="C9" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="14"/>
-      <c r="M9" s="14"/>
-      <c r="N9" s="14"/>
-      <c r="O9" s="14"/>
-      <c r="P9" s="14"/>
-      <c r="Q9" s="14"/>
-      <c r="R9" s="14"/>
-      <c r="S9" s="14"/>
-      <c r="T9" s="14"/>
-      <c r="U9" s="14"/>
-      <c r="V9" s="14"/>
-      <c r="W9" s="14"/>
-      <c r="X9" s="14"/>
-      <c r="Y9" s="14"/>
-      <c r="Z9" s="14"/>
-      <c r="AA9" s="14"/>
-      <c r="AB9" s="14"/>
-      <c r="AC9" s="14"/>
-      <c r="AD9" s="14"/>
-      <c r="AE9" s="14"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="9"/>
+      <c r="R9" s="9"/>
+      <c r="S9" s="9"/>
+      <c r="T9" s="9"/>
+      <c r="U9" s="9"/>
+      <c r="V9" s="9"/>
+      <c r="W9" s="9"/>
+      <c r="X9" s="9"/>
+      <c r="Y9" s="9"/>
+      <c r="Z9" s="9"/>
+      <c r="AA9" s="9"/>
+      <c r="AB9" s="9"/>
+      <c r="AC9" s="9"/>
+      <c r="AD9" s="9"/>
+      <c r="AE9" s="9"/>
     </row>
-    <row r="10" ht="14.25" customHeight="1">
-      <c r="B10" s="15"/>
-      <c r="C10" s="18" t="s">
+    <row r="10" spans="2:31" ht="14.25" customHeight="1">
+      <c r="B10" s="48"/>
+      <c r="C10" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="14"/>
-      <c r="L10" s="19"/>
-      <c r="M10" s="14"/>
-      <c r="N10" s="14"/>
-      <c r="O10" s="14"/>
-      <c r="P10" s="14"/>
-      <c r="Q10" s="14"/>
-      <c r="R10" s="14"/>
-      <c r="S10" s="14"/>
-      <c r="T10" s="14"/>
-      <c r="U10" s="14"/>
-      <c r="V10" s="14"/>
-      <c r="W10" s="14"/>
-      <c r="X10" s="14"/>
-      <c r="Y10" s="14"/>
-      <c r="Z10" s="14"/>
-      <c r="AA10" s="14"/>
-      <c r="AB10" s="14"/>
-      <c r="AC10" s="14"/>
-      <c r="AD10" s="14"/>
-      <c r="AE10" s="14"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="9"/>
+      <c r="O10" s="9"/>
+      <c r="P10" s="9"/>
+      <c r="Q10" s="9"/>
+      <c r="R10" s="9"/>
+      <c r="S10" s="9"/>
+      <c r="T10" s="9"/>
+      <c r="U10" s="9"/>
+      <c r="V10" s="9"/>
+      <c r="W10" s="9"/>
+      <c r="X10" s="9"/>
+      <c r="Y10" s="9"/>
+      <c r="Z10" s="9"/>
+      <c r="AA10" s="9"/>
+      <c r="AB10" s="9"/>
+      <c r="AC10" s="9"/>
+      <c r="AD10" s="9"/>
+      <c r="AE10" s="9"/>
     </row>
-    <row r="11" ht="29.25" customHeight="1">
-      <c r="B11" s="16"/>
-      <c r="C11" s="20" t="s">
+    <row r="11" spans="2:31" ht="29.25" customHeight="1">
+      <c r="B11" s="49"/>
+      <c r="C11" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="14"/>
-      <c r="L11" s="14"/>
-      <c r="M11" s="19"/>
-      <c r="N11" s="14"/>
-      <c r="O11" s="14"/>
-      <c r="P11" s="14"/>
-      <c r="Q11" s="14"/>
-      <c r="R11" s="14"/>
-      <c r="S11" s="14"/>
-      <c r="T11" s="14"/>
-      <c r="U11" s="14"/>
-      <c r="V11" s="14"/>
-      <c r="W11" s="14"/>
-      <c r="X11" s="14"/>
-      <c r="Y11" s="14"/>
-      <c r="Z11" s="14"/>
-      <c r="AA11" s="14"/>
-      <c r="AB11" s="14"/>
-      <c r="AC11" s="14"/>
-      <c r="AD11" s="14"/>
-      <c r="AE11" s="14"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="12"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="9"/>
+      <c r="P11" s="9"/>
+      <c r="Q11" s="9"/>
+      <c r="R11" s="9"/>
+      <c r="S11" s="9"/>
+      <c r="T11" s="9"/>
+      <c r="U11" s="9"/>
+      <c r="V11" s="9"/>
+      <c r="W11" s="9"/>
+      <c r="X11" s="9"/>
+      <c r="Y11" s="9"/>
+      <c r="Z11" s="9"/>
+      <c r="AA11" s="9"/>
+      <c r="AB11" s="9"/>
+      <c r="AC11" s="9"/>
+      <c r="AD11" s="9"/>
+      <c r="AE11" s="9"/>
     </row>
-    <row r="12" ht="14.25" customHeight="1">
-      <c r="B12" s="11" t="s">
+    <row r="12" spans="2:31" ht="14.25" customHeight="1">
+      <c r="B12" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="C12" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="14"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="14"/>
-      <c r="N12" s="22"/>
-      <c r="O12" s="14"/>
-      <c r="P12" s="14"/>
-      <c r="Q12" s="14"/>
-      <c r="R12" s="14"/>
-      <c r="S12" s="14"/>
-      <c r="T12" s="14"/>
-      <c r="U12" s="14"/>
-      <c r="V12" s="14"/>
-      <c r="W12" s="14"/>
-      <c r="X12" s="14"/>
-      <c r="Y12" s="14"/>
-      <c r="Z12" s="14"/>
-      <c r="AA12" s="14"/>
-      <c r="AB12" s="14"/>
-      <c r="AC12" s="14"/>
-      <c r="AD12" s="14"/>
-      <c r="AE12" s="14"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="15"/>
+      <c r="O12" s="9"/>
+      <c r="P12" s="9"/>
+      <c r="Q12" s="9"/>
+      <c r="R12" s="9"/>
+      <c r="S12" s="9"/>
+      <c r="T12" s="9"/>
+      <c r="U12" s="9"/>
+      <c r="V12" s="9"/>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
     </row>
-    <row r="13" ht="28.5" customHeight="1">
-      <c r="B13" s="15"/>
-      <c r="C13" s="23" t="s">
+    <row r="13" spans="2:31" ht="28.5" customHeight="1">
+      <c r="B13" s="48"/>
+      <c r="C13" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="14"/>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="14"/>
-      <c r="N13" s="22"/>
-      <c r="O13" s="22"/>
-      <c r="P13" s="22"/>
-      <c r="Q13" s="14"/>
-      <c r="R13" s="14"/>
-      <c r="S13" s="14"/>
-      <c r="T13" s="14"/>
-      <c r="U13" s="14"/>
-      <c r="V13" s="14"/>
-      <c r="W13" s="14"/>
-      <c r="X13" s="14"/>
-      <c r="Y13" s="14"/>
-      <c r="Z13" s="14"/>
-      <c r="AA13" s="14"/>
-      <c r="AB13" s="14"/>
-      <c r="AC13" s="14"/>
-      <c r="AD13" s="14"/>
-      <c r="AE13" s="14"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="15"/>
+      <c r="O13" s="15"/>
+      <c r="P13" s="15"/>
+      <c r="Q13" s="9"/>
+      <c r="R13" s="9"/>
+      <c r="S13" s="9"/>
+      <c r="T13" s="9"/>
+      <c r="U13" s="9"/>
+      <c r="V13" s="9"/>
+      <c r="W13" s="9"/>
+      <c r="X13" s="9"/>
+      <c r="Y13" s="9"/>
+      <c r="Z13" s="9"/>
+      <c r="AA13" s="9"/>
+      <c r="AB13" s="9"/>
+      <c r="AC13" s="9"/>
+      <c r="AD13" s="9"/>
+      <c r="AE13" s="9"/>
     </row>
-    <row r="14" ht="31.5" customHeight="1">
-      <c r="B14" s="15"/>
-      <c r="C14" s="23" t="s">
+    <row r="14" spans="2:31" ht="31.5" customHeight="1">
+      <c r="B14" s="48"/>
+      <c r="C14" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="14"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="14"/>
-      <c r="P14" s="22"/>
-      <c r="Q14" s="22"/>
-      <c r="R14" s="22"/>
-      <c r="S14" s="14"/>
-      <c r="T14" s="14"/>
-      <c r="U14" s="14"/>
-      <c r="V14" s="14"/>
-      <c r="W14" s="14"/>
-      <c r="X14" s="14"/>
-      <c r="Y14" s="14"/>
-      <c r="Z14" s="14"/>
-      <c r="AA14" s="14"/>
-      <c r="AB14" s="14"/>
-      <c r="AC14" s="14"/>
-      <c r="AD14" s="14"/>
-      <c r="AE14" s="14"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
+      <c r="P14" s="15"/>
+      <c r="Q14" s="15"/>
+      <c r="R14" s="15"/>
+      <c r="S14" s="9"/>
+      <c r="T14" s="9"/>
+      <c r="U14" s="9"/>
+      <c r="V14" s="9"/>
+      <c r="W14" s="9"/>
+      <c r="X14" s="9"/>
+      <c r="Y14" s="9"/>
+      <c r="Z14" s="9"/>
+      <c r="AA14" s="9"/>
+      <c r="AB14" s="9"/>
+      <c r="AC14" s="9"/>
+      <c r="AD14" s="9"/>
+      <c r="AE14" s="9"/>
     </row>
-    <row r="15" ht="28.5" customHeight="1">
-      <c r="B15" s="15"/>
-      <c r="C15" s="23" t="s">
+    <row r="15" spans="2:31" ht="28.5" customHeight="1">
+      <c r="B15" s="48"/>
+      <c r="C15" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="14"/>
-      <c r="O15" s="14"/>
-      <c r="P15" s="14"/>
-      <c r="Q15" s="14"/>
-      <c r="R15" s="22"/>
-      <c r="S15" s="22"/>
-      <c r="T15" s="22"/>
-      <c r="U15" s="14"/>
-      <c r="V15" s="14"/>
-      <c r="W15" s="14"/>
-      <c r="X15" s="14"/>
-      <c r="Y15" s="14"/>
-      <c r="Z15" s="14"/>
-      <c r="AA15" s="14"/>
-      <c r="AB15" s="14"/>
-      <c r="AC15" s="14"/>
-      <c r="AD15" s="14"/>
-      <c r="AE15" s="14"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="9"/>
+      <c r="P15" s="9"/>
+      <c r="Q15" s="9"/>
+      <c r="R15" s="15"/>
+      <c r="S15" s="15"/>
+      <c r="T15" s="15"/>
+      <c r="U15" s="9"/>
+      <c r="V15" s="9"/>
+      <c r="W15" s="9"/>
+      <c r="X15" s="9"/>
+      <c r="Y15" s="9"/>
+      <c r="Z15" s="9"/>
+      <c r="AA15" s="9"/>
+      <c r="AB15" s="9"/>
+      <c r="AC15" s="9"/>
+      <c r="AD15" s="9"/>
+      <c r="AE15" s="9"/>
     </row>
-    <row r="16" ht="14.25" customHeight="1">
-      <c r="B16" s="15"/>
-      <c r="C16" s="21" t="s">
+    <row r="16" spans="2:31" ht="14.25" customHeight="1">
+      <c r="B16" s="48"/>
+      <c r="C16" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="14"/>
-      <c r="M16" s="14"/>
-      <c r="N16" s="14"/>
-      <c r="O16" s="14"/>
-      <c r="P16" s="14"/>
-      <c r="Q16" s="14"/>
-      <c r="R16" s="14"/>
-      <c r="S16" s="14"/>
-      <c r="T16" s="14"/>
-      <c r="U16" s="22"/>
-      <c r="V16" s="14"/>
-      <c r="W16" s="14"/>
-      <c r="X16" s="14"/>
-      <c r="Y16" s="14"/>
-      <c r="Z16" s="14"/>
-      <c r="AA16" s="14"/>
-      <c r="AB16" s="14"/>
-      <c r="AC16" s="14"/>
-      <c r="AD16" s="14"/>
-      <c r="AE16" s="14"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="9"/>
+      <c r="P16" s="9"/>
+      <c r="Q16" s="9"/>
+      <c r="R16" s="9"/>
+      <c r="S16" s="9"/>
+      <c r="T16" s="9"/>
+      <c r="U16" s="15"/>
+      <c r="V16" s="9"/>
+      <c r="W16" s="9"/>
+      <c r="X16" s="9"/>
+      <c r="Y16" s="9"/>
+      <c r="Z16" s="9"/>
+      <c r="AA16" s="9"/>
+      <c r="AB16" s="9"/>
+      <c r="AC16" s="9"/>
+      <c r="AD16" s="9"/>
+      <c r="AE16" s="9"/>
     </row>
-    <row r="17" ht="14.25" customHeight="1">
-      <c r="B17" s="16"/>
-      <c r="C17" s="21" t="s">
+    <row r="17" spans="2:31" ht="14.25" customHeight="1">
+      <c r="B17" s="49"/>
+      <c r="C17" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="14"/>
-      <c r="K17" s="14"/>
-      <c r="L17" s="14"/>
-      <c r="M17" s="14"/>
-      <c r="N17" s="14"/>
-      <c r="O17" s="14"/>
-      <c r="P17" s="14"/>
-      <c r="Q17" s="14"/>
-      <c r="R17" s="14"/>
-      <c r="S17" s="14"/>
-      <c r="T17" s="14"/>
-      <c r="U17" s="14"/>
-      <c r="V17" s="22"/>
-      <c r="W17" s="14"/>
-      <c r="X17" s="14"/>
-      <c r="Y17" s="14"/>
-      <c r="Z17" s="14"/>
-      <c r="AA17" s="14"/>
-      <c r="AB17" s="14"/>
-      <c r="AC17" s="14"/>
-      <c r="AD17" s="14"/>
-      <c r="AE17" s="14"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="9"/>
+      <c r="P17" s="9"/>
+      <c r="Q17" s="9"/>
+      <c r="R17" s="9"/>
+      <c r="S17" s="9"/>
+      <c r="T17" s="9"/>
+      <c r="U17" s="9"/>
+      <c r="V17" s="15"/>
+      <c r="W17" s="9"/>
+      <c r="X17" s="9"/>
+      <c r="Y17" s="9"/>
+      <c r="Z17" s="9"/>
+      <c r="AA17" s="9"/>
+      <c r="AB17" s="9"/>
+      <c r="AC17" s="9"/>
+      <c r="AD17" s="9"/>
+      <c r="AE17" s="9"/>
     </row>
-    <row r="18" ht="14.25" customHeight="1">
-      <c r="B18" s="11" t="s">
+    <row r="18" spans="2:31" ht="14.25" customHeight="1">
+      <c r="B18" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="24" t="s">
+      <c r="C18" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="14"/>
-      <c r="K18" s="14"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="14"/>
-      <c r="N18" s="14"/>
-      <c r="O18" s="14"/>
-      <c r="P18" s="14"/>
-      <c r="Q18" s="14"/>
-      <c r="R18" s="14"/>
-      <c r="S18" s="14"/>
-      <c r="T18" s="14"/>
-      <c r="U18" s="14"/>
-      <c r="V18" s="14"/>
-      <c r="W18" s="25"/>
-      <c r="X18" s="14"/>
-      <c r="Y18" s="14"/>
-      <c r="Z18" s="14"/>
-      <c r="AA18" s="14"/>
-      <c r="AB18" s="14"/>
-      <c r="AC18" s="14"/>
-      <c r="AD18" s="14"/>
-      <c r="AE18" s="14"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="9"/>
+      <c r="P18" s="9"/>
+      <c r="Q18" s="9"/>
+      <c r="R18" s="9"/>
+      <c r="S18" s="9"/>
+      <c r="T18" s="9"/>
+      <c r="U18" s="9"/>
+      <c r="V18" s="9"/>
+      <c r="W18" s="18"/>
+      <c r="X18" s="9"/>
+      <c r="Y18" s="9"/>
+      <c r="Z18" s="9"/>
+      <c r="AA18" s="9"/>
+      <c r="AB18" s="9"/>
+      <c r="AC18" s="9"/>
+      <c r="AD18" s="9"/>
+      <c r="AE18" s="9"/>
     </row>
-    <row r="19" ht="14.25" customHeight="1">
-      <c r="B19" s="15"/>
-      <c r="C19" s="26" t="s">
+    <row r="19" spans="2:31" ht="14.25" customHeight="1">
+      <c r="B19" s="48"/>
+      <c r="C19" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="14"/>
-      <c r="K19" s="14"/>
-      <c r="L19" s="14"/>
-      <c r="M19" s="14"/>
-      <c r="N19" s="14"/>
-      <c r="O19" s="14"/>
-      <c r="P19" s="14"/>
-      <c r="Q19" s="14"/>
-      <c r="R19" s="14"/>
-      <c r="S19" s="14"/>
-      <c r="T19" s="14"/>
-      <c r="U19" s="14"/>
-      <c r="V19" s="14"/>
-      <c r="W19" s="14"/>
-      <c r="X19" s="25"/>
-      <c r="Y19" s="14"/>
-      <c r="Z19" s="14"/>
-      <c r="AA19" s="14"/>
-      <c r="AB19" s="14"/>
-      <c r="AC19" s="14"/>
-      <c r="AD19" s="14"/>
-      <c r="AE19" s="14"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="9"/>
+      <c r="O19" s="9"/>
+      <c r="P19" s="9"/>
+      <c r="Q19" s="9"/>
+      <c r="R19" s="9"/>
+      <c r="S19" s="9"/>
+      <c r="T19" s="9"/>
+      <c r="U19" s="9"/>
+      <c r="V19" s="9"/>
+      <c r="W19" s="9"/>
+      <c r="X19" s="18"/>
+      <c r="Y19" s="9"/>
+      <c r="Z19" s="9"/>
+      <c r="AA19" s="9"/>
+      <c r="AB19" s="9"/>
+      <c r="AC19" s="9"/>
+      <c r="AD19" s="9"/>
+      <c r="AE19" s="9"/>
     </row>
-    <row r="20" ht="14.25" customHeight="1">
-      <c r="B20" s="15"/>
-      <c r="C20" s="26" t="s">
+    <row r="20" spans="2:31" ht="14.25" customHeight="1">
+      <c r="B20" s="48"/>
+      <c r="C20" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="14"/>
-      <c r="K20" s="14"/>
-      <c r="L20" s="14"/>
-      <c r="M20" s="14"/>
-      <c r="N20" s="14"/>
-      <c r="O20" s="14"/>
-      <c r="P20" s="14"/>
-      <c r="Q20" s="14"/>
-      <c r="R20" s="14"/>
-      <c r="S20" s="14"/>
-      <c r="T20" s="14"/>
-      <c r="U20" s="14"/>
-      <c r="V20" s="14"/>
-      <c r="W20" s="14"/>
-      <c r="X20" s="14"/>
-      <c r="Y20" s="25"/>
-      <c r="Z20" s="14"/>
-      <c r="AA20" s="14"/>
-      <c r="AB20" s="14"/>
-      <c r="AC20" s="14"/>
-      <c r="AD20" s="14"/>
-      <c r="AE20" s="14"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
+      <c r="M20" s="9"/>
+      <c r="N20" s="9"/>
+      <c r="O20" s="9"/>
+      <c r="P20" s="9"/>
+      <c r="Q20" s="9"/>
+      <c r="R20" s="9"/>
+      <c r="S20" s="9"/>
+      <c r="T20" s="9"/>
+      <c r="U20" s="9"/>
+      <c r="V20" s="9"/>
+      <c r="W20" s="9"/>
+      <c r="X20" s="9"/>
+      <c r="Y20" s="18"/>
+      <c r="Z20" s="9"/>
+      <c r="AA20" s="9"/>
+      <c r="AB20" s="9"/>
+      <c r="AC20" s="9"/>
+      <c r="AD20" s="9"/>
+      <c r="AE20" s="9"/>
     </row>
-    <row r="21" ht="14.25" customHeight="1">
-      <c r="B21" s="16"/>
-      <c r="C21" s="26" t="s">
+    <row r="21" spans="2:31" ht="14.25" customHeight="1">
+      <c r="B21" s="49"/>
+      <c r="C21" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="14"/>
-      <c r="J21" s="14"/>
-      <c r="K21" s="14"/>
-      <c r="L21" s="14"/>
-      <c r="M21" s="14"/>
-      <c r="N21" s="14"/>
-      <c r="O21" s="14"/>
-      <c r="P21" s="14"/>
-      <c r="Q21" s="14"/>
-      <c r="R21" s="14"/>
-      <c r="S21" s="14"/>
-      <c r="T21" s="14"/>
-      <c r="U21" s="14"/>
-      <c r="V21" s="14"/>
-      <c r="W21" s="14"/>
-      <c r="X21" s="14"/>
-      <c r="Y21" s="14"/>
-      <c r="Z21" s="25"/>
-      <c r="AA21" s="14"/>
-      <c r="AB21" s="14"/>
-      <c r="AC21" s="14"/>
-      <c r="AD21" s="14"/>
-      <c r="AE21" s="14"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
+      <c r="M21" s="9"/>
+      <c r="N21" s="9"/>
+      <c r="O21" s="9"/>
+      <c r="P21" s="9"/>
+      <c r="Q21" s="9"/>
+      <c r="R21" s="9"/>
+      <c r="S21" s="9"/>
+      <c r="T21" s="9"/>
+      <c r="U21" s="9"/>
+      <c r="V21" s="9"/>
+      <c r="W21" s="9"/>
+      <c r="X21" s="9"/>
+      <c r="Y21" s="9"/>
+      <c r="Z21" s="18"/>
+      <c r="AA21" s="9"/>
+      <c r="AB21" s="9"/>
+      <c r="AC21" s="9"/>
+      <c r="AD21" s="9"/>
+      <c r="AE21" s="9"/>
     </row>
-    <row r="22" ht="14.25" customHeight="1">
-      <c r="B22" s="11" t="s">
+    <row r="22" spans="2:31" ht="14.25" customHeight="1">
+      <c r="B22" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="C22" s="27" t="s">
+      <c r="C22" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="14"/>
-      <c r="J22" s="14"/>
-      <c r="K22" s="14"/>
-      <c r="L22" s="14"/>
-      <c r="M22" s="14"/>
-      <c r="N22" s="14"/>
-      <c r="O22" s="14"/>
-      <c r="P22" s="14"/>
-      <c r="Q22" s="14"/>
-      <c r="R22" s="14"/>
-      <c r="S22" s="14"/>
-      <c r="T22" s="14"/>
-      <c r="U22" s="14"/>
-      <c r="V22" s="14"/>
-      <c r="W22" s="14"/>
-      <c r="X22" s="14"/>
-      <c r="Y22" s="14"/>
-      <c r="Z22" s="14"/>
-      <c r="AA22" s="28"/>
-      <c r="AB22" s="28"/>
-      <c r="AC22" s="14"/>
-      <c r="AD22" s="14"/>
-      <c r="AE22" s="14"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
+      <c r="M22" s="9"/>
+      <c r="N22" s="9"/>
+      <c r="O22" s="9"/>
+      <c r="P22" s="9"/>
+      <c r="Q22" s="9"/>
+      <c r="R22" s="9"/>
+      <c r="S22" s="9"/>
+      <c r="T22" s="9"/>
+      <c r="U22" s="9"/>
+      <c r="V22" s="9"/>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="21"/>
+      <c r="AB22" s="21"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
     </row>
-    <row r="23" ht="27.75" customHeight="1">
-      <c r="B23" s="15"/>
-      <c r="C23" s="29" t="s">
+    <row r="23" spans="2:31" ht="27.75" customHeight="1">
+      <c r="B23" s="48"/>
+      <c r="C23" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="14"/>
-      <c r="K23" s="14"/>
-      <c r="L23" s="14"/>
-      <c r="M23" s="14"/>
-      <c r="N23" s="14"/>
-      <c r="O23" s="14"/>
-      <c r="P23" s="14"/>
-      <c r="Q23" s="14"/>
-      <c r="R23" s="14"/>
-      <c r="S23" s="14"/>
-      <c r="T23" s="14"/>
-      <c r="U23" s="14"/>
-      <c r="V23" s="14"/>
-      <c r="W23" s="14"/>
-      <c r="X23" s="14"/>
-      <c r="Y23" s="14"/>
-      <c r="Z23" s="14"/>
-      <c r="AA23" s="14"/>
-      <c r="AB23" s="28"/>
-      <c r="AC23" s="28"/>
-      <c r="AD23" s="14"/>
-      <c r="AE23" s="14"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="9"/>
+      <c r="M23" s="9"/>
+      <c r="N23" s="9"/>
+      <c r="O23" s="9"/>
+      <c r="P23" s="9"/>
+      <c r="Q23" s="9"/>
+      <c r="R23" s="9"/>
+      <c r="S23" s="9"/>
+      <c r="T23" s="9"/>
+      <c r="U23" s="9"/>
+      <c r="V23" s="9"/>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="21"/>
+      <c r="AC23" s="21"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
     </row>
-    <row r="24" ht="14.25" customHeight="1">
-      <c r="B24" s="15"/>
-      <c r="C24" s="27" t="s">
+    <row r="24" spans="2:31" ht="14.25" customHeight="1">
+      <c r="B24" s="48"/>
+      <c r="C24" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="14"/>
-      <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
-      <c r="Q24" s="14"/>
-      <c r="R24" s="14"/>
-      <c r="S24" s="14"/>
-      <c r="T24" s="14"/>
-      <c r="U24" s="14"/>
-      <c r="V24" s="14"/>
-      <c r="W24" s="14"/>
-      <c r="X24" s="14"/>
-      <c r="Y24" s="14"/>
-      <c r="Z24" s="14"/>
-      <c r="AA24" s="14"/>
-      <c r="AB24" s="14"/>
-      <c r="AC24" s="14"/>
-      <c r="AD24" s="28"/>
-      <c r="AE24" s="14"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="9"/>
+      <c r="M24" s="9"/>
+      <c r="N24" s="9"/>
+      <c r="O24" s="9"/>
+      <c r="P24" s="9"/>
+      <c r="Q24" s="9"/>
+      <c r="R24" s="9"/>
+      <c r="S24" s="9"/>
+      <c r="T24" s="9"/>
+      <c r="U24" s="9"/>
+      <c r="V24" s="9"/>
+      <c r="W24" s="9"/>
+      <c r="X24" s="9"/>
+      <c r="Y24" s="9"/>
+      <c r="Z24" s="9"/>
+      <c r="AA24" s="9"/>
+      <c r="AB24" s="9"/>
+      <c r="AC24" s="9"/>
+      <c r="AD24" s="21"/>
+      <c r="AE24" s="9"/>
     </row>
-    <row r="25" ht="28.5" customHeight="1">
-      <c r="B25" s="16"/>
-      <c r="C25" s="29" t="s">
+    <row r="25" spans="2:31" ht="28.5" customHeight="1">
+      <c r="B25" s="49"/>
+      <c r="C25" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="14"/>
-      <c r="J25" s="14"/>
-      <c r="K25" s="14"/>
-      <c r="L25" s="14"/>
-      <c r="M25" s="14"/>
-      <c r="N25" s="14"/>
-      <c r="O25" s="14"/>
-      <c r="P25" s="14"/>
-      <c r="Q25" s="14"/>
-      <c r="R25" s="14"/>
-      <c r="S25" s="14"/>
-      <c r="T25" s="14"/>
-      <c r="U25" s="14"/>
-      <c r="V25" s="14"/>
-      <c r="W25" s="14"/>
-      <c r="X25" s="14"/>
-      <c r="Y25" s="14"/>
-      <c r="Z25" s="14"/>
-      <c r="AA25" s="14"/>
-      <c r="AB25" s="14"/>
-      <c r="AC25" s="14"/>
-      <c r="AD25" s="14"/>
-      <c r="AE25" s="28"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+      <c r="M25" s="9"/>
+      <c r="N25" s="9"/>
+      <c r="O25" s="9"/>
+      <c r="P25" s="9"/>
+      <c r="Q25" s="9"/>
+      <c r="R25" s="9"/>
+      <c r="S25" s="9"/>
+      <c r="T25" s="9"/>
+      <c r="U25" s="9"/>
+      <c r="V25" s="9"/>
+      <c r="W25" s="9"/>
+      <c r="X25" s="9"/>
+      <c r="Y25" s="9"/>
+      <c r="Z25" s="9"/>
+      <c r="AA25" s="9"/>
+      <c r="AB25" s="9"/>
+      <c r="AC25" s="9"/>
+      <c r="AD25" s="9"/>
+      <c r="AE25" s="21"/>
     </row>
-    <row r="26" ht="14.25" customHeight="1"/>
-    <row r="27" ht="14.25" customHeight="1"/>
-    <row r="28" ht="14.25" customHeight="1"/>
-    <row r="29" ht="14.25" customHeight="1"/>
-    <row r="30" ht="14.25" customHeight="1"/>
-    <row r="31" ht="14.25" customHeight="1"/>
-    <row r="32" ht="14.25" customHeight="1"/>
+    <row r="26" spans="2:31" ht="14.25" customHeight="1"/>
+    <row r="27" spans="2:31" ht="14.25" customHeight="1"/>
+    <row r="28" spans="2:31" ht="14.25" customHeight="1"/>
+    <row r="29" spans="2:31" ht="14.25" customHeight="1"/>
+    <row r="30" spans="2:31" ht="14.25" customHeight="1"/>
+    <row r="31" spans="2:31" ht="14.25" customHeight="1"/>
+    <row r="32" spans="2:31" ht="14.25" customHeight="1"/>
     <row r="33" ht="14.25" customHeight="1"/>
     <row r="34" ht="14.25" customHeight="1"/>
     <row r="35" ht="14.25" customHeight="1"/>
@@ -4113,544 +4626,647 @@
     <mergeCell ref="B12:B17"/>
     <mergeCell ref="B18:B21"/>
     <mergeCell ref="B22:B25"/>
+    <mergeCell ref="X2:AA2"/>
+    <mergeCell ref="AB2:AE2"/>
     <mergeCell ref="D2:G2"/>
     <mergeCell ref="H2:K2"/>
     <mergeCell ref="L2:O2"/>
     <mergeCell ref="P2:S2"/>
     <mergeCell ref="T2:W2"/>
-    <mergeCell ref="X2:AA2"/>
-    <mergeCell ref="AB2:AE2"/>
   </mergeCells>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:W1004"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10.71"/>
-    <col customWidth="1" min="2" max="2" width="23.0"/>
-    <col customWidth="1" min="3" max="3" width="10.71"/>
-    <col customWidth="1" min="4" max="4" width="16.14"/>
-    <col customWidth="1" min="5" max="5" width="13.0"/>
-    <col customWidth="1" min="6" max="6" width="10.71"/>
-    <col customWidth="1" min="7" max="8" width="22.71"/>
-    <col customWidth="1" min="9" max="10" width="10.71"/>
-    <col customWidth="1" min="11" max="11" width="22.71"/>
-    <col customWidth="1" min="12" max="13" width="10.71"/>
-    <col customWidth="1" min="14" max="14" width="15.43"/>
-    <col customWidth="1" min="15" max="15" width="18.71"/>
-    <col customWidth="1" min="16" max="16" width="10.71"/>
-    <col customWidth="1" min="17" max="17" width="23.43"/>
-    <col customWidth="1" min="18" max="18" width="21.86"/>
-    <col customWidth="1" min="19" max="19" width="22.71"/>
-    <col customWidth="1" min="20" max="20" width="23.29"/>
-    <col customWidth="1" min="21" max="26" width="10.71"/>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="2" max="2" width="23" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" customWidth="1"/>
+    <col min="4" max="4" width="16.140625" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" customWidth="1"/>
+    <col min="7" max="8" width="22.7109375" customWidth="1"/>
+    <col min="9" max="10" width="10.7109375" customWidth="1"/>
+    <col min="11" max="11" width="22.7109375" customWidth="1"/>
+    <col min="12" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="15.42578125" customWidth="1"/>
+    <col min="15" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="10.7109375" customWidth="1"/>
+    <col min="17" max="17" width="23.42578125" customWidth="1"/>
+    <col min="18" max="18" width="21.85546875" customWidth="1"/>
+    <col min="19" max="19" width="22.7109375" customWidth="1"/>
+    <col min="20" max="20" width="23.28515625" customWidth="1"/>
+    <col min="21" max="26" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1"/>
-    <row r="2" ht="14.25" customHeight="1">
-      <c r="B2" s="30" t="s">
+    <row r="1" spans="2:20" ht="14.25" customHeight="1" thickBot="1"/>
+    <row r="2" spans="2:20" ht="14.25" customHeight="1" thickBot="1">
+      <c r="B2" s="92" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="2"/>
-      <c r="G2" s="30" t="s">
+      <c r="C2" s="93"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="94"/>
+      <c r="G2" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="H2" s="9"/>
-      <c r="I2" s="2"/>
-      <c r="K2" s="31" t="s">
+      <c r="H2" s="106"/>
+      <c r="I2" s="107"/>
+      <c r="K2" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="2"/>
-      <c r="Q2" s="30" t="s">
+      <c r="L2" s="46"/>
+      <c r="M2" s="46"/>
+      <c r="N2" s="46"/>
+      <c r="O2" s="44"/>
+      <c r="Q2" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="R2" s="9"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="2"/>
+      <c r="R2" s="46"/>
+      <c r="S2" s="46"/>
+      <c r="T2" s="44"/>
     </row>
-    <row r="3" ht="57.75" customHeight="1">
-      <c r="B3" s="32"/>
-      <c r="C3" s="33" t="s">
+    <row r="3" spans="2:20" ht="57.75" customHeight="1" thickBot="1">
+      <c r="B3" s="95"/>
+      <c r="C3" s="96" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="33" t="s">
+      <c r="D3" s="96" t="s">
         <v>45</v>
       </c>
-      <c r="E3" s="33" t="s">
+      <c r="E3" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="G3" s="34" t="s">
+      <c r="G3" s="110" t="s">
         <v>47</v>
       </c>
-      <c r="H3" s="33" t="s">
+      <c r="H3" s="111" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="33" t="s">
+      <c r="I3" s="112" t="s">
         <v>49</v>
       </c>
-      <c r="K3" s="34" t="s">
+      <c r="K3" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="L3" s="33" t="s">
+      <c r="L3" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="M3" s="33" t="s">
+      <c r="M3" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="N3" s="33" t="s">
+      <c r="N3" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="O3" s="35" t="s">
+      <c r="O3" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="Q3" s="36" t="s">
+      <c r="Q3" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="R3" s="36" t="s">
+      <c r="R3" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="S3" s="36" t="s">
+      <c r="S3" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="T3" s="36" t="s">
+      <c r="T3" s="26" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="4" ht="14.25" customHeight="1">
-      <c r="B4" s="37" t="s">
+    <row r="4" spans="2:20" ht="14.25" customHeight="1" thickBot="1">
+      <c r="B4" s="98" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="38">
-        <v>1.0</v>
-      </c>
-      <c r="D4" s="39">
-        <v>45000.0</v>
-      </c>
-      <c r="E4" s="39">
-        <v>45000.0</v>
-      </c>
-      <c r="G4" s="37" t="s">
+      <c r="C4" s="31">
+        <v>1</v>
+      </c>
+      <c r="D4" s="29">
+        <v>24000</v>
+      </c>
+      <c r="E4" s="99">
+        <f>C4 * D4</f>
+        <v>24000</v>
+      </c>
+      <c r="G4" s="115" t="s">
         <v>58</v>
       </c>
-      <c r="H4" s="40" t="s">
+      <c r="H4" s="116" t="s">
         <v>59</v>
       </c>
-      <c r="I4" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K4" s="37" t="s">
+      <c r="I4" s="117">
+        <v>0</v>
+      </c>
+      <c r="K4" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="L4" s="38">
-        <v>1.0</v>
-      </c>
-      <c r="M4" s="41">
-        <v>7.0</v>
-      </c>
-      <c r="N4" s="42">
-        <v>2000000.0</v>
-      </c>
-      <c r="O4" s="43">
-        <v>1.4E7</v>
-      </c>
-      <c r="Q4" s="44" t="s">
+      <c r="L4" s="28">
+        <v>1</v>
+      </c>
+      <c r="M4" s="31">
+        <v>7</v>
+      </c>
+      <c r="N4" s="32">
+        <v>2000000</v>
+      </c>
+      <c r="O4" s="59">
+        <f>(M4*N4)*L4</f>
+        <v>14000000</v>
+      </c>
+      <c r="Q4" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="R4" s="45" t="s">
+      <c r="R4" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="S4" s="45" t="s">
+      <c r="S4" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="T4" s="45" t="s">
+      <c r="T4" s="34" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="5" ht="43.5" customHeight="1">
-      <c r="B5" s="37" t="s">
+    <row r="5" spans="2:20" ht="43.5" customHeight="1" thickBot="1">
+      <c r="B5" s="100" t="s">
+        <v>130</v>
+      </c>
+      <c r="C5" s="31">
+        <v>1</v>
+      </c>
+      <c r="D5" s="29">
+        <v>70000</v>
+      </c>
+      <c r="E5" s="99">
+        <f t="shared" ref="E5:E15" si="0">C5 * D5</f>
+        <v>70000</v>
+      </c>
+      <c r="G5" s="113" t="s">
         <v>65</v>
       </c>
-      <c r="C5" s="38">
-        <v>1.0</v>
-      </c>
-      <c r="D5" s="39">
-        <v>30000.0</v>
-      </c>
-      <c r="E5" s="39">
-        <v>30000.0</v>
-      </c>
-      <c r="G5" s="37" t="s">
+      <c r="H5" s="114" t="s">
+        <v>59</v>
+      </c>
+      <c r="I5" s="117">
+        <v>0</v>
+      </c>
+      <c r="K5" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="H5" s="40" t="s">
-        <v>59</v>
-      </c>
-      <c r="I5" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K5" s="37" t="s">
+      <c r="L5" s="28">
+        <v>1</v>
+      </c>
+      <c r="M5" s="31">
+        <v>7</v>
+      </c>
+      <c r="N5" s="35">
+        <v>2500000</v>
+      </c>
+      <c r="O5" s="59">
+        <f t="shared" ref="O5:O7" si="1">(M5*N5)*L5</f>
+        <v>17500000</v>
+      </c>
+      <c r="Q5" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="L5" s="38">
-        <v>1.0</v>
-      </c>
-      <c r="M5" s="41">
-        <v>7.0</v>
-      </c>
-      <c r="N5" s="46">
-        <v>2500000.0</v>
-      </c>
-      <c r="O5" s="47">
-        <v>1.75E7</v>
-      </c>
-      <c r="Q5" s="44" t="s">
+      <c r="R5" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="R5" s="45" t="s">
+      <c r="S5" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="S5" s="45" t="s">
+      <c r="T5" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="T5" s="45" t="s">
+    </row>
+    <row r="6" spans="2:20" ht="39.75" customHeight="1" thickBot="1">
+      <c r="B6" s="98" t="s">
+        <v>127</v>
+      </c>
+      <c r="C6" s="31">
+        <v>1</v>
+      </c>
+      <c r="D6" s="29">
+        <v>20000</v>
+      </c>
+      <c r="E6" s="99">
+        <f t="shared" si="0"/>
+        <v>20000</v>
+      </c>
+      <c r="F6" s="67"/>
+      <c r="G6" s="108" t="s">
         <v>71</v>
       </c>
+      <c r="H6" s="109" t="s">
+        <v>135</v>
+      </c>
+      <c r="I6" s="117">
+        <v>0</v>
+      </c>
+      <c r="K6" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="L6" s="28">
+        <v>1</v>
+      </c>
+      <c r="M6" s="36">
+        <v>4</v>
+      </c>
+      <c r="N6" s="37">
+        <v>1200000</v>
+      </c>
+      <c r="O6" s="59">
+        <f t="shared" si="1"/>
+        <v>4800000</v>
+      </c>
+      <c r="Q6" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="R6" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="S6" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="T6" s="34" t="s">
+        <v>76</v>
+      </c>
     </row>
-    <row r="6" ht="14.25" customHeight="1">
-      <c r="B6" s="37" t="s">
-        <v>72</v>
-      </c>
-      <c r="C6" s="38">
-        <v>1.0</v>
-      </c>
-      <c r="D6" s="39">
-        <v>20000.0</v>
-      </c>
-      <c r="E6" s="39">
-        <v>20000.0</v>
-      </c>
-      <c r="G6" s="37" t="s">
-        <v>73</v>
-      </c>
-      <c r="H6" s="40" t="s">
-        <v>74</v>
-      </c>
-      <c r="I6" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K6" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="L6" s="38">
-        <v>1.0</v>
-      </c>
-      <c r="M6" s="48">
-        <v>4.0</v>
-      </c>
-      <c r="N6" s="49">
-        <v>1200000.0</v>
-      </c>
-      <c r="O6" s="50">
-        <v>3600000.0</v>
-      </c>
-      <c r="Q6" s="44" t="s">
-        <v>76</v>
-      </c>
-      <c r="R6" s="45" t="s">
+    <row r="7" spans="2:20" ht="30.75" customHeight="1" thickBot="1">
+      <c r="B7" s="98" t="s">
+        <v>128</v>
+      </c>
+      <c r="C7" s="30">
+        <v>40</v>
+      </c>
+      <c r="D7" s="29">
+        <v>300</v>
+      </c>
+      <c r="E7" s="99">
+        <f t="shared" si="0"/>
+        <v>12000</v>
+      </c>
+      <c r="F7" s="67"/>
+      <c r="G7" s="56"/>
+      <c r="H7" s="57"/>
+      <c r="I7" s="91"/>
+      <c r="K7" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="S6" s="45" t="s">
+      <c r="L7" s="28">
+        <v>1</v>
+      </c>
+      <c r="M7" s="38">
+        <v>7</v>
+      </c>
+      <c r="N7" s="37">
+        <v>1800000</v>
+      </c>
+      <c r="O7" s="59">
+        <f t="shared" si="1"/>
+        <v>12600000</v>
+      </c>
+      <c r="Q7" s="33" t="s">
         <v>78</v>
       </c>
-      <c r="T6" s="45" t="s">
+      <c r="R7" s="34" t="s">
         <v>79</v>
       </c>
+      <c r="S7" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="T7" s="34" t="s">
+        <v>81</v>
+      </c>
     </row>
-    <row r="7" ht="14.25" customHeight="1">
-      <c r="B7" s="37" t="s">
-        <v>80</v>
-      </c>
-      <c r="C7" s="40" t="s">
-        <v>81</v>
-      </c>
-      <c r="D7" s="39">
-        <v>25000.0</v>
-      </c>
-      <c r="E7" s="39">
-        <v>25000.0</v>
-      </c>
-      <c r="G7" s="37" t="s">
+    <row r="8" spans="2:20" ht="33.75" customHeight="1" thickBot="1">
+      <c r="B8" s="100" t="s">
+        <v>129</v>
+      </c>
+      <c r="C8" s="30">
+        <v>40</v>
+      </c>
+      <c r="D8" s="29">
+        <v>300</v>
+      </c>
+      <c r="E8" s="99">
+        <f t="shared" si="0"/>
+        <v>12000</v>
+      </c>
+      <c r="K8" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="H7" s="40" t="s">
+      <c r="L8" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="I7" s="51">
-        <v>240000.0</v>
-      </c>
-      <c r="K7" s="37" t="s">
+      <c r="M8" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="N8" s="39" t="s">
+        <v>83</v>
+      </c>
+      <c r="O8" s="60">
+        <f>SUM(O4:O7)</f>
+        <v>48900000</v>
+      </c>
+      <c r="Q8" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="L7" s="38">
-        <v>1.0</v>
-      </c>
-      <c r="M7" s="52">
-        <v>7.0</v>
-      </c>
-      <c r="N7" s="49">
-        <v>1800000.0</v>
-      </c>
-      <c r="O7" s="53">
-        <v>1.26E7</v>
-      </c>
-      <c r="Q7" s="44" t="s">
+      <c r="R8" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="R7" s="45" t="s">
+      <c r="S8" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="S7" s="45" t="s">
+      <c r="T8" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="T7" s="45" t="s">
+    </row>
+    <row r="9" spans="2:20" ht="60" customHeight="1" thickBot="1">
+      <c r="B9" s="101" t="s">
+        <v>131</v>
+      </c>
+      <c r="C9" s="102">
+        <v>3</v>
+      </c>
+      <c r="D9" s="103">
+        <v>3333</v>
+      </c>
+      <c r="E9" s="104">
+        <f t="shared" si="0"/>
+        <v>9999</v>
+      </c>
+      <c r="K9" s="56"/>
+      <c r="L9" s="57"/>
+      <c r="M9" s="57"/>
+      <c r="N9" s="57"/>
+      <c r="O9" s="58"/>
+      <c r="Q9" s="61" t="s">
+        <v>89</v>
+      </c>
+      <c r="R9" s="62" t="s">
+        <v>90</v>
+      </c>
+      <c r="S9" s="62" t="s">
+        <v>91</v>
+      </c>
+      <c r="T9" s="62" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="2:20" ht="53.25" customHeight="1" thickBot="1">
+      <c r="B10" s="55" t="s">
+        <v>133</v>
+      </c>
+      <c r="C10" s="30">
+        <v>1</v>
+      </c>
+      <c r="D10" s="29">
+        <v>2400</v>
+      </c>
+      <c r="E10" s="86">
+        <f t="shared" si="0"/>
+        <v>2400</v>
+      </c>
+      <c r="K10" s="56"/>
+      <c r="L10" s="57"/>
+      <c r="M10" s="57"/>
+      <c r="N10" s="57"/>
+      <c r="O10" s="58"/>
+      <c r="Q10" s="61" t="s">
+        <v>94</v>
+      </c>
+      <c r="R10" s="62" t="s">
+        <v>95</v>
+      </c>
+      <c r="S10" s="62" t="s">
+        <v>96</v>
+      </c>
+      <c r="T10" s="62" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" spans="2:20" ht="53.25" customHeight="1" thickBot="1">
+      <c r="B11" s="55" t="s">
+        <v>134</v>
+      </c>
+      <c r="C11" s="30">
+        <v>1</v>
+      </c>
+      <c r="D11" s="29">
+        <v>1300</v>
+      </c>
+      <c r="E11" s="86">
+        <f t="shared" si="0"/>
+        <v>1300</v>
+      </c>
+      <c r="K11" s="56"/>
+      <c r="L11" s="57"/>
+      <c r="M11" s="57"/>
+      <c r="N11" s="57"/>
+      <c r="O11" s="58"/>
+      <c r="Q11" s="63"/>
+      <c r="R11" s="88"/>
+      <c r="S11" s="89"/>
+      <c r="T11" s="90"/>
+    </row>
+    <row r="12" spans="2:20" ht="59.25" customHeight="1" thickBot="1">
+      <c r="B12" s="55" t="s">
+        <v>132</v>
+      </c>
+      <c r="C12" s="30">
+        <v>6</v>
+      </c>
+      <c r="D12" s="29">
+        <v>383</v>
+      </c>
+      <c r="E12" s="86">
+        <f>C12 * D12</f>
+        <v>2298</v>
+      </c>
+      <c r="K12" s="56"/>
+      <c r="L12" s="57"/>
+      <c r="M12" s="57"/>
+      <c r="N12" s="57"/>
+      <c r="O12" s="58"/>
+      <c r="Q12" s="63" t="s">
+        <v>98</v>
+      </c>
+      <c r="R12" s="74" t="s">
+        <v>99</v>
+      </c>
+      <c r="S12" s="75"/>
+      <c r="T12" s="76"/>
+    </row>
+    <row r="13" spans="2:20" ht="14.25" customHeight="1" thickBot="1">
+      <c r="B13" s="27" t="s">
         <v>88</v>
       </c>
+      <c r="C13" s="28">
+        <v>1</v>
+      </c>
+      <c r="D13" s="29">
+        <v>20000</v>
+      </c>
+      <c r="E13" s="86">
+        <f t="shared" si="0"/>
+        <v>20000</v>
+      </c>
+      <c r="Q13" s="77" t="s">
+        <v>101</v>
+      </c>
+      <c r="R13" s="78">
+        <v>7000000</v>
+      </c>
+      <c r="S13" s="78"/>
+      <c r="T13" s="78"/>
     </row>
-    <row r="8" ht="14.25" customHeight="1">
-      <c r="B8" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="C8" s="40" t="s">
-        <v>81</v>
-      </c>
-      <c r="D8" s="39">
-        <v>15000.0</v>
-      </c>
-      <c r="E8" s="39">
-        <v>15000.0</v>
-      </c>
-      <c r="K8" s="37" t="s">
-        <v>90</v>
-      </c>
-      <c r="L8" s="40" t="s">
-        <v>91</v>
-      </c>
-      <c r="M8" s="40" t="s">
-        <v>91</v>
-      </c>
-      <c r="N8" s="54" t="s">
-        <v>91</v>
-      </c>
-      <c r="O8" s="55">
-        <v>4.47E7</v>
-      </c>
-      <c r="Q8" s="44" t="s">
-        <v>92</v>
-      </c>
-      <c r="R8" s="45" t="s">
+    <row r="14" spans="2:20" ht="32.25" customHeight="1" thickBot="1">
+      <c r="B14" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="S8" s="45" t="s">
-        <v>94</v>
-      </c>
-      <c r="T8" s="45" t="s">
-        <v>95</v>
-      </c>
+      <c r="C14" s="41">
+        <v>2</v>
+      </c>
+      <c r="D14" s="53">
+        <v>3500000</v>
+      </c>
+      <c r="E14" s="86">
+        <f t="shared" si="0"/>
+        <v>7000000</v>
+      </c>
+      <c r="Q14" s="68"/>
+      <c r="R14" s="69"/>
+      <c r="S14" s="69"/>
+      <c r="T14" s="70"/>
     </row>
-    <row r="9" ht="14.25" customHeight="1">
-      <c r="B9" s="37" t="s">
-        <v>96</v>
-      </c>
-      <c r="C9" s="38">
-        <v>1.0</v>
-      </c>
-      <c r="D9" s="39">
-        <v>20000.0</v>
-      </c>
-      <c r="E9" s="39">
-        <v>20000.0</v>
-      </c>
-      <c r="Q9" s="44" t="s">
+    <row r="15" spans="2:20" ht="53.25" customHeight="1" thickBot="1">
+      <c r="B15" s="33" t="s">
         <v>97</v>
       </c>
-      <c r="R9" s="45" t="s">
+      <c r="C15" s="87">
+        <v>2</v>
+      </c>
+      <c r="D15" s="85">
+        <v>450000</v>
+      </c>
+      <c r="E15" s="86">
+        <f t="shared" si="0"/>
+        <v>900000</v>
+      </c>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="69"/>
+      <c r="S15" s="72"/>
+      <c r="T15" s="72"/>
+    </row>
+    <row r="16" spans="2:20" ht="14.25" customHeight="1" thickBot="1">
+      <c r="B16" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="C16" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="E16" s="54">
+        <f>SUM(E4:E15)</f>
+        <v>8073997</v>
+      </c>
+      <c r="Q16" s="68"/>
+      <c r="R16" s="73"/>
+      <c r="S16" s="67"/>
+      <c r="T16" s="67"/>
+    </row>
+    <row r="17" spans="17:23" ht="14.25" customHeight="1">
+      <c r="Q17" s="67"/>
+      <c r="R17" s="67"/>
+      <c r="S17" s="67"/>
+      <c r="T17" s="67"/>
+    </row>
+    <row r="18" spans="17:23" ht="14.25" customHeight="1">
+      <c r="Q18" s="64" t="s">
+        <v>102</v>
+      </c>
+      <c r="R18" s="65"/>
+      <c r="S18" s="66"/>
+      <c r="T18" s="67"/>
+    </row>
+    <row r="19" spans="17:23" ht="14.25" customHeight="1">
+      <c r="Q19" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="R19" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="S19" s="26" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="20" spans="17:23" ht="14.25" customHeight="1">
+      <c r="Q20" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="R20" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="S20" s="34" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="17:23" ht="14.25" customHeight="1">
+      <c r="Q21" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="R21" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="S21" s="34" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="22" spans="17:23" ht="14.25" customHeight="1">
+      <c r="Q22" s="33" t="s">
+        <v>112</v>
+      </c>
+      <c r="R22" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="S22" s="34" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="23" spans="17:23" ht="69" customHeight="1">
+      <c r="Q23" s="42" t="s">
         <v>98</v>
       </c>
-      <c r="S9" s="45" t="s">
-        <v>99</v>
-      </c>
-      <c r="T9" s="45" t="s">
-        <v>100</v>
-      </c>
+      <c r="R23" s="81" t="s">
+        <v>115</v>
+      </c>
+      <c r="S23" s="82"/>
+      <c r="W23" s="79"/>
     </row>
-    <row r="10" ht="14.25" customHeight="1">
-      <c r="B10" s="56" t="s">
+    <row r="24" spans="17:23" ht="14.25" customHeight="1">
+      <c r="Q24" s="80" t="s">
         <v>101</v>
       </c>
-      <c r="C10" s="57">
-        <v>3.0</v>
-      </c>
-      <c r="D10" s="58" t="str">
-        <f>S4</f>
-        <v>$3.500.000 – $6.000.000</v>
-      </c>
-      <c r="E10" s="59" t="str">
-        <f>R12</f>
-        <v>$10'500.000 </v>
-      </c>
-      <c r="Q10" s="44" t="s">
-        <v>102</v>
-      </c>
-      <c r="R10" s="45" t="s">
-        <v>103</v>
-      </c>
-      <c r="S10" s="45" t="s">
-        <v>104</v>
-      </c>
-      <c r="T10" s="45" t="s">
-        <v>105</v>
-      </c>
+      <c r="R24" s="83">
+        <v>900000</v>
+      </c>
+      <c r="S24" s="84"/>
     </row>
-    <row r="11" ht="53.25" customHeight="1">
-      <c r="B11" s="44" t="s">
-        <v>106</v>
-      </c>
-      <c r="C11" s="60">
-        <v>1.0</v>
-      </c>
-      <c r="D11" s="61">
-        <f>R20</f>
-        <v>450000</v>
-      </c>
-      <c r="E11" s="61">
-        <f>D11</f>
-        <v>450000</v>
-      </c>
-      <c r="Q11" s="62" t="s">
-        <v>107</v>
-      </c>
-      <c r="R11" s="63" t="s">
-        <v>108</v>
-      </c>
-      <c r="S11" s="9"/>
-      <c r="T11" s="2"/>
-    </row>
-    <row r="12" ht="14.25" customHeight="1">
-      <c r="B12" s="37" t="s">
-        <v>109</v>
-      </c>
-      <c r="C12" s="40" t="s">
-        <v>91</v>
-      </c>
-      <c r="D12" s="40" t="s">
-        <v>91</v>
-      </c>
-      <c r="E12" s="64">
-        <v>1.1105E7</v>
-      </c>
-      <c r="Q12" s="44" t="s">
-        <v>110</v>
-      </c>
-      <c r="R12" s="65" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="13" ht="14.25" customHeight="1"/>
-    <row r="14" ht="14.25" customHeight="1">
-      <c r="Q14" s="30" t="s">
-        <v>112</v>
-      </c>
-      <c r="R14" s="9"/>
-      <c r="S14" s="2"/>
-    </row>
-    <row r="15" ht="14.25" customHeight="1">
-      <c r="Q15" s="36" t="s">
-        <v>113</v>
-      </c>
-      <c r="R15" s="36" t="s">
-        <v>114</v>
-      </c>
-      <c r="S15" s="36" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="16" ht="14.25" customHeight="1">
-      <c r="Q16" s="44" t="s">
-        <v>116</v>
-      </c>
-      <c r="R16" s="45" t="s">
-        <v>117</v>
-      </c>
-      <c r="S16" s="45" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="17" ht="14.25" customHeight="1">
-      <c r="Q17" s="44" t="s">
-        <v>119</v>
-      </c>
-      <c r="R17" s="45" t="s">
-        <v>120</v>
-      </c>
-      <c r="S17" s="45" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="18" ht="14.25" customHeight="1">
-      <c r="Q18" s="44" t="s">
-        <v>122</v>
-      </c>
-      <c r="R18" s="45" t="s">
-        <v>123</v>
-      </c>
-      <c r="S18" s="45" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="19" ht="69.0" customHeight="1">
-      <c r="Q19" s="62" t="s">
-        <v>107</v>
-      </c>
-      <c r="R19" s="63" t="s">
-        <v>125</v>
-      </c>
-      <c r="S19" s="2"/>
-    </row>
-    <row r="20" ht="14.25" customHeight="1">
-      <c r="Q20" s="44" t="s">
-        <v>110</v>
-      </c>
-      <c r="R20" s="66">
-        <v>450000.0</v>
-      </c>
-      <c r="S20" s="67"/>
-    </row>
-    <row r="21" ht="14.25" customHeight="1"/>
-    <row r="22" ht="14.25" customHeight="1"/>
-    <row r="23" ht="14.25" customHeight="1"/>
-    <row r="24" ht="14.25" customHeight="1"/>
-    <row r="25" ht="14.25" customHeight="1"/>
-    <row r="26" ht="14.25" customHeight="1"/>
-    <row r="27" ht="14.25" customHeight="1"/>
-    <row r="28" ht="14.25" customHeight="1"/>
-    <row r="29" ht="14.25" customHeight="1"/>
-    <row r="30" ht="14.25" customHeight="1"/>
-    <row r="31" ht="14.25" customHeight="1"/>
-    <row r="32" ht="14.25" customHeight="1"/>
+    <row r="25" spans="17:23" ht="14.25" customHeight="1"/>
+    <row r="26" spans="17:23" ht="14.25" customHeight="1"/>
+    <row r="27" spans="17:23" ht="14.25" customHeight="1"/>
+    <row r="28" spans="17:23" ht="14.25" customHeight="1"/>
+    <row r="29" spans="17:23" ht="14.25" customHeight="1"/>
+    <row r="30" spans="17:23" ht="14.25" customHeight="1"/>
+    <row r="31" spans="17:23" ht="14.25" customHeight="1"/>
+    <row r="32" spans="17:23" ht="14.25" customHeight="1"/>
     <row r="33" ht="14.25" customHeight="1"/>
     <row r="34" ht="14.25" customHeight="1"/>
     <row r="35" ht="14.25" customHeight="1"/>
@@ -5619,144 +6235,146 @@
     <row r="998" ht="14.25" customHeight="1"/>
     <row r="999" ht="14.25" customHeight="1"/>
     <row r="1000" ht="14.25" customHeight="1"/>
+    <row r="1001" ht="14.25" customHeight="1"/>
+    <row r="1002" ht="14.25" customHeight="1"/>
+    <row r="1003" ht="14.25" customHeight="1"/>
+    <row r="1004" ht="14.25" customHeight="1"/>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="9">
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="Q18:S18"/>
+    <mergeCell ref="R23:S23"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="G2:I2"/>
     <mergeCell ref="K2:O2"/>
     <mergeCell ref="Q2:T2"/>
-    <mergeCell ref="R11:T11"/>
-    <mergeCell ref="Q14:S14"/>
-    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="R12:T12"/>
+    <mergeCell ref="R13:T13"/>
   </mergeCells>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup orientation="portrait"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:H1000"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10.71"/>
-    <col customWidth="1" min="2" max="2" width="11.57"/>
-    <col customWidth="1" min="3" max="3" width="21.29"/>
-    <col customWidth="1" min="4" max="4" width="22.86"/>
-    <col customWidth="1" min="5" max="5" width="10.71"/>
-    <col customWidth="1" min="6" max="6" width="23.43"/>
-    <col customWidth="1" min="7" max="7" width="22.86"/>
-    <col customWidth="1" min="8" max="8" width="23.29"/>
-    <col customWidth="1" min="9" max="26" width="10.71"/>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" customWidth="1"/>
+    <col min="3" max="3" width="21.28515625" customWidth="1"/>
+    <col min="4" max="4" width="22.85546875" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" customWidth="1"/>
+    <col min="6" max="6" width="23.42578125" customWidth="1"/>
+    <col min="7" max="7" width="22.85546875" customWidth="1"/>
+    <col min="8" max="8" width="23.28515625" customWidth="1"/>
+    <col min="9" max="26" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1"/>
-    <row r="2" ht="14.25" customHeight="1">
-      <c r="B2" s="30" t="s">
+    <row r="1" spans="2:8" ht="14.25" customHeight="1"/>
+    <row r="2" spans="2:8" ht="14.25" customHeight="1">
+      <c r="B2" s="50" t="s">
+        <v>116</v>
+      </c>
+      <c r="C2" s="46"/>
+      <c r="D2" s="44"/>
+      <c r="F2" s="52" t="s">
+        <v>117</v>
+      </c>
+      <c r="G2" s="46"/>
+      <c r="H2" s="44"/>
+    </row>
+    <row r="3" spans="2:8" ht="14.25" customHeight="1">
+      <c r="B3" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="G3" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="H3" s="26" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" ht="14.25" customHeight="1">
+      <c r="B4" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="C4" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="D4" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="F4" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="G4" s="34" t="s">
+        <v>119</v>
+      </c>
+      <c r="H4" s="34" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" ht="14.25" customHeight="1">
+      <c r="B5" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="D5" s="34" t="s">
+        <v>111</v>
+      </c>
+      <c r="F5" s="33" t="s">
+        <v>121</v>
+      </c>
+      <c r="G5" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="H5" s="34" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" ht="14.25" customHeight="1">
+      <c r="B6" s="33" t="s">
+        <v>112</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="F6" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="G6" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="H6" s="34" t="s">
         <v>126</v>
       </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="2"/>
-      <c r="F2" s="68" t="s">
-        <v>127</v>
-      </c>
-      <c r="G2" s="9"/>
-      <c r="H2" s="2"/>
     </row>
-    <row r="3" ht="14.25" customHeight="1">
-      <c r="B3" s="36" t="s">
-        <v>113</v>
-      </c>
-      <c r="C3" s="36" t="s">
-        <v>114</v>
-      </c>
-      <c r="D3" s="36" t="s">
-        <v>115</v>
-      </c>
-      <c r="F3" s="36" t="s">
-        <v>113</v>
-      </c>
-      <c r="G3" s="36" t="s">
-        <v>114</v>
-      </c>
-      <c r="H3" s="36" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="4" ht="14.25" customHeight="1">
-      <c r="B4" s="44" t="s">
-        <v>116</v>
-      </c>
-      <c r="C4" s="45" t="s">
-        <v>117</v>
-      </c>
-      <c r="D4" s="45" t="s">
-        <v>118</v>
-      </c>
-      <c r="F4" s="44" t="s">
-        <v>128</v>
-      </c>
-      <c r="G4" s="45" t="s">
-        <v>129</v>
-      </c>
-      <c r="H4" s="45" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="5" ht="14.25" customHeight="1">
-      <c r="B5" s="44" t="s">
-        <v>119</v>
-      </c>
-      <c r="C5" s="45" t="s">
-        <v>120</v>
-      </c>
-      <c r="D5" s="45" t="s">
-        <v>121</v>
-      </c>
-      <c r="F5" s="44" t="s">
-        <v>131</v>
-      </c>
-      <c r="G5" s="45" t="s">
-        <v>132</v>
-      </c>
-      <c r="H5" s="45" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="6" ht="14.25" customHeight="1">
-      <c r="B6" s="44" t="s">
-        <v>122</v>
-      </c>
-      <c r="C6" s="45" t="s">
-        <v>123</v>
-      </c>
-      <c r="D6" s="45" t="s">
-        <v>124</v>
-      </c>
-      <c r="F6" s="44" t="s">
-        <v>134</v>
-      </c>
-      <c r="G6" s="45" t="s">
-        <v>135</v>
-      </c>
-      <c r="H6" s="45" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="7" ht="14.25" customHeight="1"/>
-    <row r="8" ht="14.25" customHeight="1"/>
-    <row r="9" ht="14.25" customHeight="1"/>
-    <row r="10" ht="14.25" customHeight="1"/>
-    <row r="11" ht="14.25" customHeight="1"/>
-    <row r="12" ht="14.25" customHeight="1"/>
-    <row r="13" ht="14.25" customHeight="1"/>
-    <row r="14" ht="14.25" customHeight="1"/>
-    <row r="15" ht="14.25" customHeight="1"/>
-    <row r="16" ht="14.25" customHeight="1"/>
+    <row r="7" spans="2:8" ht="14.25" customHeight="1"/>
+    <row r="8" spans="2:8" ht="14.25" customHeight="1"/>
+    <row r="9" spans="2:8" ht="14.25" customHeight="1"/>
+    <row r="10" spans="2:8" ht="14.25" customHeight="1"/>
+    <row r="11" spans="2:8" ht="14.25" customHeight="1"/>
+    <row r="12" spans="2:8" ht="14.25" customHeight="1"/>
+    <row r="13" spans="2:8" ht="14.25" customHeight="1"/>
+    <row r="14" spans="2:8" ht="14.25" customHeight="1"/>
+    <row r="15" spans="2:8" ht="14.25" customHeight="1"/>
+    <row r="16" spans="2:8" ht="14.25" customHeight="1"/>
     <row r="17" ht="14.25" customHeight="1"/>
     <row r="18" ht="14.25" customHeight="1"/>
     <row r="19" ht="14.25" customHeight="1"/>
@@ -6746,9 +7364,7 @@
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="F2:H2"/>
   </mergeCells>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>